--- a/notebooks/extra_analysis/ema_rwd_final_statistics_tables_logit_vif_due_result.xlsx
+++ b/notebooks/extra_analysis/ema_rwd_final_statistics_tables_logit_vif_due_result.xlsx
@@ -536,20 +536,28 @@
           <t>298 (69.6)</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>1.061291630104257</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.268641624687713</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.8060020732672145</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.240691597661026</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -567,20 +575,28 @@
           <t>64 (64.6)</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>1.061291630104257</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.268641624687713</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9003272470899936</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.110707249205403</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -623,20 +639,28 @@
           <t>86 (59.7)</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>1.079924649233619</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.166237248022355</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8577494723333011</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.165841579919298</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -679,20 +703,28 @@
           <t>13 (32.5)</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>1.134157542232404</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.737707727065248</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.7024536695972079</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.423581430748888</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -710,20 +742,28 @@
           <t>5 (35.7)</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>1.134157542232404</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.737707727065248</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.95020059667357</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.05240935808793</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -741,20 +781,28 @@
           <t>149 (60.6)</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>1.134157542232404</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.737707727065248</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5838007054517281</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.712913312131456</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -772,20 +820,28 @@
           <t>7 (31.8)</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1.134157542232404</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.737707727065248</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.8975816164401061</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.114104814185138</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -828,20 +884,28 @@
           <t>848 (70.2)</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>1.071451653064425</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.148008644854489</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.8709407167603517</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.148183775033175</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -884,20 +948,28 @@
           <t>61 (45.2)</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>1.175928788866047</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.382808516483968</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.7230620646304181</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.383007142701</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -919,20 +991,28 @@
           <t>440 (76.3)</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>1.122930136478577</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.260972091411795</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.7929086690946396</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.261179299681288</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -975,20 +1055,28 @@
           <t>191 (51.2)</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>1.09332342734018</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.708015960647026</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5412699475350268</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.847506968665183</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1006,20 +1094,28 @@
           <t>259 (66.4)</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>1.09332342734018</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
-      <c r="G19" t="n">
-        <v>1.708015960647026</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.4820857525943667</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.074319754563278</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1037,20 +1133,28 @@
           <t>278 (70.7)</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>1.09332342734018</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
-      <c r="G20" t="n">
-        <v>1.708015960647026</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.4637173731172342</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.15648595021948</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1114,20 +1218,28 @@
           <t>232 (66.9)</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>1.067974689275552</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
-      <c r="G23" t="n">
-        <v>1.692340240299077</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.5764737148956091</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.73468446897199</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1145,20 +1257,28 @@
           <t>92 (63.0)</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>1.067974689275552</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
-      <c r="G24" t="n">
-        <v>1.692340240299077</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.7394811290952037</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.352299552557285</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1176,20 +1296,28 @@
           <t>123 (73.2)</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>1.067974689275552</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="G25" t="n">
-        <v>1.692340240299077</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.6714057495175845</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.489412327372108</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1207,20 +1335,28 @@
           <t>337 (67.3)</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>1.067974689275552</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F26" t="n">
         <v>4</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.692340240299077</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.4456101343568479</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.244114132285853</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1263,20 +1399,28 @@
           <t>204 (69.6)</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>1.041902387752062</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
       </c>
       <c r="F28" t="n">
         <v>4</v>
       </c>
-      <c r="G28" t="n">
-        <v>1.388725040670991</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.5927231306145548</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.68712835445306</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1294,20 +1438,28 @@
           <t>204 (69.4)</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>1.041902387752062</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
       </c>
       <c r="F29" t="n">
         <v>4</v>
       </c>
-      <c r="G29" t="n">
-        <v>1.388725040670991</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.5728838781309001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.74555444510433</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1325,20 +1477,28 @@
           <t>227 (76.9)</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>1.041902387752062</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
       </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.388725040670991</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.5288897193527603</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.89075333365105</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1356,20 +1516,28 @@
           <t>181 (59.7)</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>1.041902387752062</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
       </c>
       <c r="F31" t="n">
         <v>4</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.388725040670991</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.5491412091659794</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1.821025235965759</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1391,20 +1559,28 @@
           <t>61 (89.7)</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>1.073239868827368</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F32" t="n">
         <v>5</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.027533203901888</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.8391268303418922</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.191714963508629</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1422,20 +1598,28 @@
           <t>17 (89.5)</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>1.073239868827368</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F33" t="n">
         <v>5</v>
       </c>
-      <c r="G33" t="n">
-        <v>2.027533203901888</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.9489935190661432</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.053747976049457</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1453,20 +1637,28 @@
           <t>304 (75.8)</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>1.073239868827368</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F34" t="n">
         <v>5</v>
       </c>
-      <c r="G34" t="n">
-        <v>2.027533203901888</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.6780679714926621</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1.474778402818016</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1484,20 +1676,28 @@
           <t>56 (69.1)</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>1.073239868827368</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F35" t="n">
         <v>5</v>
       </c>
-      <c r="G35" t="n">
-        <v>2.027533203901888</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.8724157135503368</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1.146242536061682</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1536,20 +1736,28 @@
           <t>29 (48.3)</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>1.073239868827368</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F37" t="n">
         <v>5</v>
       </c>
-      <c r="G37" t="n">
-        <v>2.027533203901888</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.8132176496869061</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.229683099456838</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1571,20 +1779,28 @@
           <t>267 (66.4)</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>1.074031342553127</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
-      <c r="G38" t="n">
-        <v>1.153543324786473</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.8668438356655089</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1.153610326169375</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1627,20 +1843,28 @@
           <t>12 (57.1)</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>1.043970871358167</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
       </c>
       <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" t="n">
-        <v>1.187827908512611</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.8982183418769152</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1.113315052006622</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1679,20 +1903,28 @@
           <t>12 (52.2)</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>1.043970871358167</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
       </c>
       <c r="F42" t="n">
         <v>2</v>
       </c>
-      <c r="G42" t="n">
-        <v>1.187827908512611</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.935523073034939</v>
-      </c>
-      <c r="I42" t="n">
-        <v>1.068920723415074</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1735,20 +1967,28 @@
           <t>330 (65.9)</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>1.19066577219764</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" t="n">
-        <v>1.417684981083002</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.7076150207826309</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1.41319781326008</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
       </c>
     </row>
   </sheetData>
